--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>6769788</v>
       </c>
       <c r="B3" t="n">
-        <v>96332</v>
+        <v>98238</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,16 +830,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nipbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507791.093435063</v>
+        <v>507791</v>
       </c>
       <c r="R3" t="n">
-        <v>6926204.189847669</v>
+        <v>6926204</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +882,9 @@
           <t>2002-07-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>6769788</v>
       </c>
       <c r="B3" t="n">
-        <v>98238</v>
+        <v>98239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -870,11 +870,6 @@
       <c r="W3" t="inlineStr">
         <is>
           <t>Haverö</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Y-Ång-0056</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">

--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>6769788</v>
       </c>
       <c r="B3" t="n">
-        <v>98239</v>
+        <v>98242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>6769788</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98353</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>6769788</v>
       </c>
       <c r="B3" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>6769788</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98363</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6769788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960145</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134957069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968134</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971219</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134959840</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971438</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134965186</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,6 +1612,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134968339</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1669,8 +1719,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62732455</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40965-2021 artfynd.xlsx
+++ b/artfynd/A 40965-2021 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>134960145</v>
       </c>
       <c r="B3" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>134957069</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>134968134</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>134971219</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>134959840</v>
       </c>
       <c r="B7" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>134971438</v>
       </c>
       <c r="B8" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>134965186</v>
       </c>
       <c r="B9" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>134968339</v>
       </c>
       <c r="B10" t="n">
-        <v>98252</v>
+        <v>98296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
